--- a/output/graficos_dimensiones/comunal_o_ocup_a_2022_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2022_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 22:45</t>
+    <t xml:space="preserve">2026-08-17 13:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2022_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2022_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 13:57</t>
+    <t xml:space="preserve">2026-08-17 21:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_o_ocup_a_2022_o higgins.xlsx
+++ b/output/graficos_dimensiones/comunal_o_ocup_a_2022_o higgins.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 21:43</t>
+    <t xml:space="preserve">2026-09-06 19:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
